--- a/DateBase/orders/Dang Nguyen48_2026-5-6.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-6.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>496_大飞燕深蓝色_delphinium dark blue_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01112595105550</v>
+        <v>01112595105555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-6.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-6.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,9 +524,93 @@
         <v>5</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>495_大飞燕深粉色_delphinium pink_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>402_大飞燕深紫色_delphinium purple_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>403_大飞燕浅蓝色_delphinium light blue_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="C16" t="str" xml:space="preserve">
+        <v xml:space="preserve">404_小飞燕白色_ delphinium ballkleid
+white_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="C17" t="str" xml:space="preserve">
+        <v xml:space="preserve">497_小飞燕粉色_delphinium ballkleid
+pink_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="C18" t="str" xml:space="preserve">
+        <v xml:space="preserve">499_小飞燕浅蓝_delphinium ballkleid
+light blue_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="C19" t="str" xml:space="preserve">
+        <v xml:space="preserve">405_小飞燕浅蓝_ delphinium ballkleid
+dark blue_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>3</v>
+      </c>
+      <c r="C20" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +665,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01112595105555</v>
+        <v>01112595105555551010555570</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-6.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-6.xlsx
@@ -607,6 +607,9 @@
       <c r="C21" t="str">
         <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -665,7 +668,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01112595105555551010555570</v>
+        <v>011125951055555510105555710</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-6.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-6.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -611,9 +611,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>4</v>
+      </c>
+      <c r="C23" t="str">
+        <v>356_绿枫叶山货_maple leaf small_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>109_绣球国产绿_Hydrangea Colombia Green (local)_Hydrangea L._1stem</v>
+      </c>
+      <c r="F24" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>457_茴香花_lace flower yellow_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>563_星芹_Astrantia_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>878_玛格丽特粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L29"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -668,7 +735,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>011125951055555510105555710</v>
+        <v>011125951055555510105555710103205551010</v>
       </c>
     </row>
   </sheetData>
